--- a/dist/xlsx/urban-zones.xlsx
+++ b/dist/xlsx/urban-zones.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F192"/>
+  <dimension ref="A1:G192"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -418,6 +418,9 @@
       <c r="F1" t="str">
         <v>district_id</v>
       </c>
+      <c r="G1" t="str">
+        <v>city_id</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2">
@@ -438,6 +441,9 @@
       <c r="F2">
         <v>1000001002</v>
       </c>
+      <c r="G2">
+        <v>1000001001101</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3">
@@ -458,6 +464,9 @@
       <c r="F3">
         <v>1000001002</v>
       </c>
+      <c r="G3">
+        <v>1000001001101</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4">
@@ -478,6 +487,9 @@
       <c r="F4">
         <v>1000001002</v>
       </c>
+      <c r="G4">
+        <v>1000001001101</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5">
@@ -498,6 +510,9 @@
       <c r="F5">
         <v>1000001002</v>
       </c>
+      <c r="G5">
+        <v>1000001001101</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6">
@@ -518,6 +533,9 @@
       <c r="F6">
         <v>1000001002</v>
       </c>
+      <c r="G6">
+        <v>1000001001101</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7">
@@ -538,6 +556,9 @@
       <c r="F7">
         <v>1000006003</v>
       </c>
+      <c r="G7">
+        <v>1000006001110</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8">
@@ -558,6 +579,9 @@
       <c r="F8">
         <v>1000006003</v>
       </c>
+      <c r="G8">
+        <v>1000006001110</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9">
@@ -578,6 +602,9 @@
       <c r="F9">
         <v>1010003001</v>
       </c>
+      <c r="G9">
+        <v>1010003001120</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10">
@@ -598,6 +625,9 @@
       <c r="F10">
         <v>1010003001</v>
       </c>
+      <c r="G10">
+        <v>1010003001120</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11">
@@ -618,6 +648,9 @@
       <c r="F11">
         <v>1010005005</v>
       </c>
+      <c r="G11">
+        <v>1010005001129</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12">
@@ -638,6 +671,9 @@
       <c r="F12">
         <v>1010005005</v>
       </c>
+      <c r="G12">
+        <v>1010005001129</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13">
@@ -658,6 +694,9 @@
       <c r="F13">
         <v>1010005005</v>
       </c>
+      <c r="G13">
+        <v>1010005001129</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14">
@@ -678,6 +717,9 @@
       <c r="F14">
         <v>1010005005</v>
       </c>
+      <c r="G14">
+        <v>1010005001129</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15">
@@ -698,6 +740,9 @@
       <c r="F15">
         <v>1010005005</v>
       </c>
+      <c r="G15">
+        <v>1010005001129</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16">
@@ -718,6 +763,9 @@
       <c r="F16">
         <v>1020002002</v>
       </c>
+      <c r="G16">
+        <v>1020002001154</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17">
@@ -738,6 +786,9 @@
       <c r="F17">
         <v>1020002002</v>
       </c>
+      <c r="G17">
+        <v>1020002001154</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18">
@@ -758,6 +809,9 @@
       <c r="F18">
         <v>1020007003</v>
       </c>
+      <c r="G18">
+        <v>1020007001169</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19">
@@ -778,6 +832,9 @@
       <c r="F19">
         <v>1020007003</v>
       </c>
+      <c r="G19">
+        <v>1020007001169</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20">
@@ -798,6 +855,9 @@
       <c r="F20">
         <v>1020007003</v>
       </c>
+      <c r="G20">
+        <v>1020007001169</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21">
@@ -818,6 +878,9 @@
       <c r="F21">
         <v>1030003003</v>
       </c>
+      <c r="G21">
+        <v>1030003001214</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22">
@@ -838,6 +901,9 @@
       <c r="F22">
         <v>1030003003</v>
       </c>
+      <c r="G22">
+        <v>1030003001214</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23">
@@ -858,6 +924,9 @@
       <c r="F23">
         <v>1030003003</v>
       </c>
+      <c r="G23">
+        <v>1030003001214</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24">
@@ -878,6 +947,9 @@
       <c r="F24">
         <v>1030003003</v>
       </c>
+      <c r="G24">
+        <v>1030003001214</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25">
@@ -898,6 +970,9 @@
       <c r="F25">
         <v>1030003003</v>
       </c>
+      <c r="G25">
+        <v>1030003001214</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26">
@@ -918,6 +993,9 @@
       <c r="F26">
         <v>1030003003</v>
       </c>
+      <c r="G26">
+        <v>1030003001214</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27">
@@ -938,6 +1016,9 @@
       <c r="F27">
         <v>1030003003</v>
       </c>
+      <c r="G27">
+        <v>1030003001214</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28">
@@ -958,6 +1039,9 @@
       <c r="F28">
         <v>1030003003</v>
       </c>
+      <c r="G28">
+        <v>1030003001214</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29">
@@ -978,6 +1062,9 @@
       <c r="F29">
         <v>1030003003</v>
       </c>
+      <c r="G29">
+        <v>1030003001214</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30">
@@ -998,6 +1085,9 @@
       <c r="F30">
         <v>1030003003</v>
       </c>
+      <c r="G30">
+        <v>1030003001214</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31">
@@ -1018,6 +1108,9 @@
       <c r="F31">
         <v>1030006002</v>
       </c>
+      <c r="G31">
+        <v>1030006001223</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32">
@@ -1038,6 +1131,9 @@
       <c r="F32">
         <v>1030006002</v>
       </c>
+      <c r="G32">
+        <v>1030006001223</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33">
@@ -1058,6 +1154,9 @@
       <c r="F33">
         <v>1040001004</v>
       </c>
+      <c r="G33">
+        <v>1040001001235</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34">
@@ -1078,6 +1177,9 @@
       <c r="F34">
         <v>1040001004</v>
       </c>
+      <c r="G34">
+        <v>1040001001235</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35">
@@ -1098,6 +1200,9 @@
       <c r="F35">
         <v>1040001004</v>
       </c>
+      <c r="G35">
+        <v>1040001001235</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36">
@@ -1118,6 +1223,9 @@
       <c r="F36">
         <v>1040001004</v>
       </c>
+      <c r="G36">
+        <v>1040001001235</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37">
@@ -1138,6 +1246,9 @@
       <c r="F37">
         <v>1040001004</v>
       </c>
+      <c r="G37">
+        <v>1040001001235</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38">
@@ -1158,6 +1269,9 @@
       <c r="F38">
         <v>1050002004</v>
       </c>
+      <c r="G38">
+        <v>1050002001258</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39">
@@ -1178,6 +1292,9 @@
       <c r="F39">
         <v>1050002004</v>
       </c>
+      <c r="G39">
+        <v>1050002001258</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40">
@@ -1198,6 +1315,9 @@
       <c r="F40">
         <v>1050002004</v>
       </c>
+      <c r="G40">
+        <v>1050002001258</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41">
@@ -1218,6 +1338,9 @@
       <c r="F41">
         <v>1050002004</v>
       </c>
+      <c r="G41">
+        <v>1050002001258</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42">
@@ -1238,6 +1361,9 @@
       <c r="F42">
         <v>1050002004</v>
       </c>
+      <c r="G42">
+        <v>1050002001258</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43">
@@ -1258,6 +1384,9 @@
       <c r="F43">
         <v>1050002004</v>
       </c>
+      <c r="G43">
+        <v>1050002001258</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44">
@@ -1278,6 +1407,9 @@
       <c r="F44">
         <v>1050002004</v>
       </c>
+      <c r="G44">
+        <v>1050002001258</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45">
@@ -1298,6 +1430,9 @@
       <c r="F45">
         <v>1050002004</v>
       </c>
+      <c r="G45">
+        <v>1050002001258</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46">
@@ -1318,6 +1453,9 @@
       <c r="F46">
         <v>1060001002</v>
       </c>
+      <c r="G46">
+        <v>1060001001270</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47">
@@ -1338,6 +1476,9 @@
       <c r="F47">
         <v>1060001002</v>
       </c>
+      <c r="G47">
+        <v>1060001001270</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48">
@@ -1358,6 +1499,9 @@
       <c r="F48">
         <v>1060001002</v>
       </c>
+      <c r="G48">
+        <v>1060001001270</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49">
@@ -1378,6 +1522,9 @@
       <c r="F49">
         <v>1060003002</v>
       </c>
+      <c r="G49">
+        <v>1060003001272</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50">
@@ -1398,6 +1545,9 @@
       <c r="F50">
         <v>1060003002</v>
       </c>
+      <c r="G50">
+        <v>1060003001272</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51">
@@ -1418,6 +1568,9 @@
       <c r="F51">
         <v>1060003002</v>
       </c>
+      <c r="G51">
+        <v>1060003001272</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52">
@@ -1438,6 +1591,9 @@
       <c r="F52">
         <v>1060003002</v>
       </c>
+      <c r="G52">
+        <v>1060003001272</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53">
@@ -1458,6 +1614,9 @@
       <c r="F53">
         <v>1060003002</v>
       </c>
+      <c r="G53">
+        <v>1060003001272</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54">
@@ -1478,6 +1637,9 @@
       <c r="F54">
         <v>1060003002</v>
       </c>
+      <c r="G54">
+        <v>1060003001272</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55">
@@ -1498,6 +1660,9 @@
       <c r="F55">
         <v>1060003002</v>
       </c>
+      <c r="G55">
+        <v>1060003001272</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56">
@@ -1518,6 +1683,9 @@
       <c r="F56">
         <v>1060003002</v>
       </c>
+      <c r="G56">
+        <v>1060003001272</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57">
@@ -1538,6 +1706,9 @@
       <c r="F57">
         <v>1060008002</v>
       </c>
+      <c r="G57">
+        <v>1060008001282</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58">
@@ -1558,6 +1729,9 @@
       <c r="F58">
         <v>1060008002</v>
       </c>
+      <c r="G58">
+        <v>1060008001282</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59">
@@ -1578,6 +1752,9 @@
       <c r="F59">
         <v>1060008002</v>
       </c>
+      <c r="G59">
+        <v>1060008001282</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60">
@@ -1598,6 +1775,9 @@
       <c r="F60">
         <v>1070007005</v>
       </c>
+      <c r="G60">
+        <v>1070007001309</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61">
@@ -1618,6 +1798,9 @@
       <c r="F61">
         <v>1070007005</v>
       </c>
+      <c r="G61">
+        <v>1070007001309</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62">
@@ -1638,6 +1821,9 @@
       <c r="F62">
         <v>1070007005</v>
       </c>
+      <c r="G62">
+        <v>1070007001309</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63">
@@ -1658,6 +1844,9 @@
       <c r="F63">
         <v>1070007005</v>
       </c>
+      <c r="G63">
+        <v>1070007001309</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64">
@@ -1678,6 +1867,9 @@
       <c r="F64">
         <v>1070007005</v>
       </c>
+      <c r="G64">
+        <v>1070007001309</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65">
@@ -1698,6 +1890,9 @@
       <c r="F65">
         <v>1070007005</v>
       </c>
+      <c r="G65">
+        <v>1070007001309</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66">
@@ -1718,6 +1913,9 @@
       <c r="F66">
         <v>1070007005</v>
       </c>
+      <c r="G66">
+        <v>1070007001309</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67">
@@ -1738,6 +1936,9 @@
       <c r="F67">
         <v>1070007005</v>
       </c>
+      <c r="G67">
+        <v>1070007001309</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68">
@@ -1758,6 +1959,9 @@
       <c r="F68">
         <v>1070007005</v>
       </c>
+      <c r="G68">
+        <v>1070007001309</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69">
@@ -1778,6 +1982,9 @@
       <c r="F69">
         <v>1070007005</v>
       </c>
+      <c r="G69">
+        <v>1070007001309</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70">
@@ -1798,6 +2005,9 @@
       <c r="F70">
         <v>1080006001</v>
       </c>
+      <c r="G70">
+        <v>1080006001338</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71">
@@ -1818,6 +2028,9 @@
       <c r="F71">
         <v>1080006001</v>
       </c>
+      <c r="G71">
+        <v>1080006001338</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72">
@@ -1838,6 +2051,9 @@
       <c r="F72">
         <v>1080008005</v>
       </c>
+      <c r="G72">
+        <v>1080008001346</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73">
@@ -1858,6 +2074,9 @@
       <c r="F73">
         <v>1080008005</v>
       </c>
+      <c r="G73">
+        <v>1080008001346</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74">
@@ -1878,6 +2097,9 @@
       <c r="F74">
         <v>1080008005</v>
       </c>
+      <c r="G74">
+        <v>1080008001346</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75">
@@ -1898,6 +2120,9 @@
       <c r="F75">
         <v>1080008005</v>
       </c>
+      <c r="G75">
+        <v>1080008001346</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76">
@@ -1918,6 +2143,9 @@
       <c r="F76">
         <v>1100002003</v>
       </c>
+      <c r="G76">
+        <v>1100002001406</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77">
@@ -1938,6 +2166,9 @@
       <c r="F77">
         <v>1100002003</v>
       </c>
+      <c r="G77">
+        <v>1100002001406</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78">
@@ -1958,6 +2189,9 @@
       <c r="F78">
         <v>1100002003</v>
       </c>
+      <c r="G78">
+        <v>1100002001406</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79">
@@ -1978,6 +2212,9 @@
       <c r="F79">
         <v>1100002003</v>
       </c>
+      <c r="G79">
+        <v>1100002001406</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80">
@@ -1998,6 +2235,9 @@
       <c r="F80">
         <v>1100002003</v>
       </c>
+      <c r="G80">
+        <v>1100002001406</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81">
@@ -2018,6 +2258,9 @@
       <c r="F81">
         <v>1100002003</v>
       </c>
+      <c r="G81">
+        <v>1100002001406</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82">
@@ -2038,6 +2281,9 @@
       <c r="F82">
         <v>1100002003</v>
       </c>
+      <c r="G82">
+        <v>1100002001406</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83">
@@ -2058,6 +2304,9 @@
       <c r="F83">
         <v>1100002003</v>
       </c>
+      <c r="G83">
+        <v>1100002001406</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84">
@@ -2078,6 +2327,9 @@
       <c r="F84">
         <v>1100002003</v>
       </c>
+      <c r="G84">
+        <v>1100002001406</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85">
@@ -2098,6 +2350,9 @@
       <c r="F85">
         <v>1100002003</v>
       </c>
+      <c r="G85">
+        <v>1100002001406</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86">
@@ -2118,6 +2373,9 @@
       <c r="F86">
         <v>1100002003</v>
       </c>
+      <c r="G86">
+        <v>1100002001406</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87">
@@ -2138,6 +2396,9 @@
       <c r="F87">
         <v>1100002003</v>
       </c>
+      <c r="G87">
+        <v>1100002001406</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88">
@@ -2158,6 +2419,9 @@
       <c r="F88">
         <v>1100002003</v>
       </c>
+      <c r="G88">
+        <v>1100002001406</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89">
@@ -2178,6 +2442,9 @@
       <c r="F89">
         <v>1100002003</v>
       </c>
+      <c r="G89">
+        <v>1100002001406</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90">
@@ -2198,6 +2465,9 @@
       <c r="F90">
         <v>1100002003</v>
       </c>
+      <c r="G90">
+        <v>1100002001406</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91">
@@ -2218,6 +2488,9 @@
       <c r="F91">
         <v>1110005001</v>
       </c>
+      <c r="G91">
+        <v>1110005001451</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92">
@@ -2238,6 +2511,9 @@
       <c r="F92">
         <v>1110005001</v>
       </c>
+      <c r="G92">
+        <v>1110005001451</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93">
@@ -2258,6 +2534,9 @@
       <c r="F93">
         <v>1110005001</v>
       </c>
+      <c r="G93">
+        <v>1110005001451</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94">
@@ -2278,6 +2557,9 @@
       <c r="F94">
         <v>1110005001</v>
       </c>
+      <c r="G94">
+        <v>1110005001451</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95">
@@ -2298,6 +2580,9 @@
       <c r="F95">
         <v>1110005001</v>
       </c>
+      <c r="G95">
+        <v>1110005001451</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96">
@@ -2318,6 +2603,9 @@
       <c r="F96">
         <v>1120004003</v>
       </c>
+      <c r="G96">
+        <v>1120004001458</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97">
@@ -2338,6 +2626,9 @@
       <c r="F97">
         <v>1120004003</v>
       </c>
+      <c r="G97">
+        <v>1120004001458</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98">
@@ -2358,6 +2649,9 @@
       <c r="F98">
         <v>1120004003</v>
       </c>
+      <c r="G98">
+        <v>1120004001458</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99">
@@ -2378,6 +2672,9 @@
       <c r="F99">
         <v>1130004007</v>
       </c>
+      <c r="G99">
+        <v>1130004001475</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100">
@@ -2398,6 +2695,9 @@
       <c r="F100">
         <v>1130004007</v>
       </c>
+      <c r="G100">
+        <v>1130004001475</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101">
@@ -2418,6 +2718,9 @@
       <c r="F101">
         <v>1130004007</v>
       </c>
+      <c r="G101">
+        <v>1130004001475</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102">
@@ -2438,6 +2741,9 @@
       <c r="F102">
         <v>1130004007</v>
       </c>
+      <c r="G102">
+        <v>1130004001475</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103">
@@ -2458,6 +2764,9 @@
       <c r="F103">
         <v>1150002002</v>
       </c>
+      <c r="G103">
+        <v>1150002001492</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104">
@@ -2478,6 +2787,9 @@
       <c r="F104">
         <v>1160001003</v>
       </c>
+      <c r="G104">
+        <v>1160001001500</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105">
@@ -2498,6 +2810,9 @@
       <c r="F105">
         <v>1160001003</v>
       </c>
+      <c r="G105">
+        <v>1160001001500</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106">
@@ -2518,6 +2833,9 @@
       <c r="F106">
         <v>1190004005</v>
       </c>
+      <c r="G106">
+        <v>1190004001534</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107">
@@ -2538,6 +2856,9 @@
       <c r="F107">
         <v>1190004005</v>
       </c>
+      <c r="G107">
+        <v>1190004001534</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108">
@@ -2558,6 +2879,9 @@
       <c r="F108">
         <v>1190004005</v>
       </c>
+      <c r="G108">
+        <v>1190004001534</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109">
@@ -2578,6 +2902,9 @@
       <c r="F109">
         <v>1190004005</v>
       </c>
+      <c r="G109">
+        <v>1190004001534</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110">
@@ -2598,6 +2925,9 @@
       <c r="F110">
         <v>1210005003</v>
       </c>
+      <c r="G110">
+        <v>1210005001562</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111">
@@ -2618,6 +2948,9 @@
       <c r="F111">
         <v>1210005003</v>
       </c>
+      <c r="G111">
+        <v>1210005001562</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112">
@@ -2638,6 +2971,9 @@
       <c r="F112">
         <v>1210005003</v>
       </c>
+      <c r="G112">
+        <v>1210005001562</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113">
@@ -2658,6 +2994,9 @@
       <c r="F113">
         <v>1210005003</v>
       </c>
+      <c r="G113">
+        <v>1210005001562</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114">
@@ -2678,6 +3017,9 @@
       <c r="F114">
         <v>1220002004</v>
       </c>
+      <c r="G114">
+        <v>1220002001567</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115">
@@ -2698,6 +3040,9 @@
       <c r="F115">
         <v>1220002004</v>
       </c>
+      <c r="G115">
+        <v>1220002001567</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116">
@@ -2718,6 +3063,9 @@
       <c r="F116">
         <v>1220002004</v>
       </c>
+      <c r="G116">
+        <v>1220002001567</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117">
@@ -2738,6 +3086,9 @@
       <c r="F117">
         <v>1220002004</v>
       </c>
+      <c r="G117">
+        <v>1220002001567</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118">
@@ -2758,6 +3109,9 @@
       <c r="F118">
         <v>1230001002</v>
       </c>
+      <c r="G118">
+        <v>1230001001576</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119">
@@ -2778,6 +3132,9 @@
       <c r="F119">
         <v>1230001002</v>
       </c>
+      <c r="G119">
+        <v>1230001001576</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120">
@@ -2798,6 +3155,9 @@
       <c r="F120">
         <v>1230001002</v>
       </c>
+      <c r="G120">
+        <v>1230001001576</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121">
@@ -2818,6 +3178,9 @@
       <c r="F121">
         <v>1230001002</v>
       </c>
+      <c r="G121">
+        <v>1230001001576</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122">
@@ -2838,6 +3201,9 @@
       <c r="F122">
         <v>1230001002</v>
       </c>
+      <c r="G122">
+        <v>1230001001576</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123">
@@ -2858,6 +3224,9 @@
       <c r="F123">
         <v>1230001002</v>
       </c>
+      <c r="G123">
+        <v>1230001001576</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124">
@@ -2878,6 +3247,9 @@
       <c r="F124">
         <v>1230001002</v>
       </c>
+      <c r="G124">
+        <v>1230001001576</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125">
@@ -2898,6 +3270,9 @@
       <c r="F125">
         <v>1230001002</v>
       </c>
+      <c r="G125">
+        <v>1230001001576</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126">
@@ -2918,6 +3293,9 @@
       <c r="F126">
         <v>1230001002</v>
       </c>
+      <c r="G126">
+        <v>1230001001576</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127">
@@ -2938,6 +3316,9 @@
       <c r="F127">
         <v>1230001002</v>
       </c>
+      <c r="G127">
+        <v>1230001001576</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128">
@@ -2958,6 +3339,9 @@
       <c r="F128">
         <v>1230001002</v>
       </c>
+      <c r="G128">
+        <v>1230001001576</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129">
@@ -2978,6 +3362,9 @@
       <c r="F129">
         <v>1230001002</v>
       </c>
+      <c r="G129">
+        <v>1230001001576</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130">
@@ -2998,6 +3385,9 @@
       <c r="F130">
         <v>1230001002</v>
       </c>
+      <c r="G130">
+        <v>1230001001576</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131">
@@ -3018,6 +3408,9 @@
       <c r="F131">
         <v>1230001002</v>
       </c>
+      <c r="G131">
+        <v>1230001001576</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132">
@@ -3038,6 +3431,9 @@
       <c r="F132">
         <v>1230001002</v>
       </c>
+      <c r="G132">
+        <v>1230001001576</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133">
@@ -3058,6 +3454,9 @@
       <c r="F133">
         <v>1230001002</v>
       </c>
+      <c r="G133">
+        <v>1230001001576</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134">
@@ -3078,6 +3477,9 @@
       <c r="F134">
         <v>1230001002</v>
       </c>
+      <c r="G134">
+        <v>1230001001576</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135">
@@ -3098,6 +3500,9 @@
       <c r="F135">
         <v>1230001002</v>
       </c>
+      <c r="G135">
+        <v>1230001001576</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136">
@@ -3118,6 +3523,9 @@
       <c r="F136">
         <v>1230001002</v>
       </c>
+      <c r="G136">
+        <v>1230001001576</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137">
@@ -3138,6 +3546,9 @@
       <c r="F137">
         <v>1230001002</v>
       </c>
+      <c r="G137">
+        <v>1230001001576</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138">
@@ -3158,6 +3569,9 @@
       <c r="F138">
         <v>1230001002</v>
       </c>
+      <c r="G138">
+        <v>1230001001576</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139">
@@ -3178,6 +3592,9 @@
       <c r="F139">
         <v>1230001002</v>
       </c>
+      <c r="G139">
+        <v>1230001001576</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140">
@@ -3198,6 +3615,9 @@
       <c r="F140">
         <v>1240001001</v>
       </c>
+      <c r="G140">
+        <v>1240001001195</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141">
@@ -3218,6 +3638,9 @@
       <c r="F141">
         <v>1240001001</v>
       </c>
+      <c r="G141">
+        <v>1240001001195</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142">
@@ -3238,6 +3661,9 @@
       <c r="F142">
         <v>1240001001</v>
       </c>
+      <c r="G142">
+        <v>1240001001195</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143">
@@ -3258,6 +3684,9 @@
       <c r="F143">
         <v>1240001001</v>
       </c>
+      <c r="G143">
+        <v>1240001001195</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144">
@@ -3278,6 +3707,9 @@
       <c r="F144">
         <v>1240001001</v>
       </c>
+      <c r="G144">
+        <v>1240001001195</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145">
@@ -3298,6 +3730,9 @@
       <c r="F145">
         <v>1250001003</v>
       </c>
+      <c r="G145">
+        <v>1250001001114</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146">
@@ -3318,6 +3753,9 @@
       <c r="F146">
         <v>1250001003</v>
       </c>
+      <c r="G146">
+        <v>1250001001114</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147">
@@ -3338,6 +3776,9 @@
       <c r="F147">
         <v>1250001003</v>
       </c>
+      <c r="G147">
+        <v>1250001001114</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148">
@@ -3358,6 +3799,9 @@
       <c r="F148">
         <v>1250001003</v>
       </c>
+      <c r="G148">
+        <v>1250001001114</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149">
@@ -3378,6 +3822,9 @@
       <c r="F149">
         <v>1250001003</v>
       </c>
+      <c r="G149">
+        <v>1250001001114</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150">
@@ -3398,6 +3845,9 @@
       <c r="F150">
         <v>1250001003</v>
       </c>
+      <c r="G150">
+        <v>1250001001114</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151">
@@ -3418,6 +3868,9 @@
       <c r="F151">
         <v>1250001003</v>
       </c>
+      <c r="G151">
+        <v>1250001001114</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152">
@@ -3438,6 +3891,9 @@
       <c r="F152">
         <v>1250001003</v>
       </c>
+      <c r="G152">
+        <v>1250001001114</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153">
@@ -3458,6 +3914,9 @@
       <c r="F153">
         <v>1260003005</v>
       </c>
+      <c r="G153">
+        <v>1260003001595</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154">
@@ -3478,6 +3937,9 @@
       <c r="F154">
         <v>1260003005</v>
       </c>
+      <c r="G154">
+        <v>1260003001595</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155">
@@ -3498,6 +3960,9 @@
       <c r="F155">
         <v>1260003005</v>
       </c>
+      <c r="G155">
+        <v>1260003001595</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156">
@@ -3518,6 +3983,9 @@
       <c r="F156">
         <v>1260003005</v>
       </c>
+      <c r="G156">
+        <v>1260003001595</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157">
@@ -3538,6 +4006,9 @@
       <c r="F157">
         <v>1270005002</v>
       </c>
+      <c r="G157">
+        <v>1270005001181</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158">
@@ -3558,6 +4029,9 @@
       <c r="F158">
         <v>1270005002</v>
       </c>
+      <c r="G158">
+        <v>1270005001181</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159">
@@ -3578,6 +4052,9 @@
       <c r="F159">
         <v>1270005002</v>
       </c>
+      <c r="G159">
+        <v>1270005001181</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160">
@@ -3598,6 +4075,9 @@
       <c r="F160">
         <v>1270006004</v>
       </c>
+      <c r="G160">
+        <v>1270006001186</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161">
@@ -3618,6 +4098,9 @@
       <c r="F161">
         <v>1270006004</v>
       </c>
+      <c r="G161">
+        <v>1270006001186</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162">
@@ -3638,6 +4121,9 @@
       <c r="F162">
         <v>1300001001</v>
       </c>
+      <c r="G162">
+        <v>1300001001590</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163">
@@ -3658,6 +4144,9 @@
       <c r="F163">
         <v>1300001001</v>
       </c>
+      <c r="G163">
+        <v>1300001001590</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164">
@@ -3678,6 +4167,9 @@
       <c r="F164">
         <v>1300001001</v>
       </c>
+      <c r="G164">
+        <v>1300001001590</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165">
@@ -3698,6 +4190,9 @@
       <c r="F165">
         <v>1300001001</v>
       </c>
+      <c r="G165">
+        <v>1300001001590</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166">
@@ -3718,6 +4213,9 @@
       <c r="F166">
         <v>1300001001</v>
       </c>
+      <c r="G166">
+        <v>1300001001590</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167">
@@ -3738,6 +4236,9 @@
       <c r="F167">
         <v>1300001001</v>
       </c>
+      <c r="G167">
+        <v>1300001001590</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168">
@@ -3758,6 +4259,9 @@
       <c r="F168">
         <v>1300001001</v>
       </c>
+      <c r="G168">
+        <v>1300001001590</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169">
@@ -3778,6 +4282,9 @@
       <c r="F169">
         <v>1300001001</v>
       </c>
+      <c r="G169">
+        <v>1300001001590</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170">
@@ -3798,6 +4305,9 @@
       <c r="F170">
         <v>1300001001</v>
       </c>
+      <c r="G170">
+        <v>1300001001590</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171">
@@ -3818,6 +4328,9 @@
       <c r="F171">
         <v>1300001001</v>
       </c>
+      <c r="G171">
+        <v>1300001001590</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172">
@@ -3838,6 +4351,9 @@
       <c r="F172">
         <v>1300006001</v>
       </c>
+      <c r="G172">
+        <v>1300006002282</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173">
@@ -3858,6 +4374,9 @@
       <c r="F173">
         <v>1300006001</v>
       </c>
+      <c r="G173">
+        <v>1300006002282</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174">
@@ -3878,6 +4397,9 @@
       <c r="F174">
         <v>10600013003</v>
       </c>
+      <c r="G174">
+        <v>10600013001291</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175">
@@ -3898,6 +4420,9 @@
       <c r="F175">
         <v>10600013003</v>
       </c>
+      <c r="G175">
+        <v>10600013001291</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176">
@@ -3918,6 +4443,9 @@
       <c r="F176">
         <v>10900016005</v>
       </c>
+      <c r="G176">
+        <v>10900016001392</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177">
@@ -3938,6 +4466,9 @@
       <c r="F177">
         <v>10900016005</v>
       </c>
+      <c r="G177">
+        <v>10900016001392</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178">
@@ -3958,6 +4489,9 @@
       <c r="F178">
         <v>10900016005</v>
       </c>
+      <c r="G178">
+        <v>10900016001392</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179">
@@ -3978,6 +4512,9 @@
       <c r="F179">
         <v>10900016005</v>
       </c>
+      <c r="G179">
+        <v>10900016001392</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180">
@@ -3998,6 +4535,9 @@
       <c r="F180">
         <v>10900016005</v>
       </c>
+      <c r="G180">
+        <v>10900016001392</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181">
@@ -4018,6 +4558,9 @@
       <c r="F181">
         <v>10900016005</v>
       </c>
+      <c r="G181">
+        <v>10900016001392</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182">
@@ -4038,6 +4581,9 @@
       <c r="F182">
         <v>10900016005</v>
       </c>
+      <c r="G182">
+        <v>10900016001392</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183">
@@ -4058,6 +4604,9 @@
       <c r="F183">
         <v>10900016005</v>
       </c>
+      <c r="G183">
+        <v>10900016001392</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184">
@@ -4078,6 +4627,9 @@
       <c r="F184">
         <v>10900016005</v>
       </c>
+      <c r="G184">
+        <v>10900016001392</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185">
@@ -4098,6 +4650,9 @@
       <c r="F185">
         <v>10900016005</v>
       </c>
+      <c r="G185">
+        <v>10900016001392</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186">
@@ -4118,6 +4673,9 @@
       <c r="F186">
         <v>10900016005</v>
       </c>
+      <c r="G186">
+        <v>10900016001392</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187">
@@ -4138,6 +4696,9 @@
       <c r="F187">
         <v>10900016005</v>
       </c>
+      <c r="G187">
+        <v>10900016001392</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188">
@@ -4158,6 +4719,9 @@
       <c r="F188">
         <v>10900017004</v>
       </c>
+      <c r="G188">
+        <v>10900017001394</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189">
@@ -4178,6 +4742,9 @@
       <c r="F189">
         <v>10900017004</v>
       </c>
+      <c r="G189">
+        <v>10900017001394</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190">
@@ -4198,6 +4765,9 @@
       <c r="F190">
         <v>12300010002</v>
       </c>
+      <c r="G190">
+        <v>12300010001581</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191">
@@ -4218,6 +4788,9 @@
       <c r="F191">
         <v>12300013002</v>
       </c>
+      <c r="G191">
+        <v>12300013002120</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192">
@@ -4238,10 +4811,13 @@
       <c r="F192">
         <v>12300013002</v>
       </c>
+      <c r="G192">
+        <v>12300013002120</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F192"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G192"/>
   </ignoredErrors>
 </worksheet>
 </file>